--- a/artfynd/A 21628-2021 artfynd.xlsx
+++ b/artfynd/A 21628-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120474544</v>
+        <v>120474545</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750779</v>
+        <v>750807</v>
       </c>
       <c r="R2" t="n">
-        <v>7079695</v>
+        <v>7079863</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spår i levande gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120474545</v>
+        <v>120474512</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750807</v>
+        <v>750695</v>
       </c>
       <c r="R4" t="n">
-        <v>7079863</v>
+        <v>7080057</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,12 +949,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar på gammal levande gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120474515</v>
+        <v>120474513</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750770</v>
+        <v>750669</v>
       </c>
       <c r="R5" t="n">
-        <v>7079880</v>
+        <v>7080068</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,12 +1056,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i död gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120474516</v>
+        <v>120474515</v>
       </c>
       <c r="B6" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750762</v>
+        <v>750770</v>
       </c>
       <c r="R6" t="n">
-        <v>7079867</v>
+        <v>7079880</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flera kroppar på nyligen död gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120474512</v>
+        <v>120474521</v>
       </c>
       <c r="B7" t="n">
-        <v>90738</v>
+        <v>97059</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750695</v>
+        <v>750817</v>
       </c>
       <c r="R7" t="n">
-        <v>7080057</v>
+        <v>7079478</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar på gammal levande gran.</t>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120474521</v>
+        <v>120474516</v>
       </c>
       <c r="B8" t="n">
-        <v>97059</v>
+        <v>90738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,25 +1314,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>750817</v>
+        <v>750762</v>
       </c>
       <c r="R8" t="n">
-        <v>7079478</v>
+        <v>7079867</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 kvm</t>
+          <t>Flera kroppar på nyligen död gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120474513</v>
+        <v>120474519</v>
       </c>
       <c r="B9" t="n">
         <v>57372</v>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750669</v>
+        <v>750771</v>
       </c>
       <c r="R9" t="n">
-        <v>7080068</v>
+        <v>7079698</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,17 +1479,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre hackspår i död gran</t>
+          <t>Flera spår i levande gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120474519</v>
+        <v>120474544</v>
       </c>
       <c r="B10" t="n">
         <v>57372</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750771</v>
+        <v>750779</v>
       </c>
       <c r="R10" t="n">
-        <v>7079698</v>
+        <v>7079695</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flera spår i levande gran</t>
+          <t>Spår i levande gran</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 21628-2021 artfynd.xlsx
+++ b/artfynd/A 21628-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120474521</v>
+        <v>120474544</v>
       </c>
       <c r="B2" t="n">
-        <v>97067</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750817</v>
+        <v>750779</v>
       </c>
       <c r="R2" t="n">
-        <v>7079478</v>
+        <v>7079695</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1 kvm</t>
+          <t>Spår i levande gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120474515</v>
+        <v>120474521</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>97067</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750770</v>
+        <v>750817</v>
       </c>
       <c r="R3" t="n">
-        <v>7079880</v>
+        <v>7079478</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120474520</v>
+        <v>120474512</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750809</v>
+        <v>750695</v>
       </c>
       <c r="R5" t="n">
-        <v>7079547</v>
+        <v>7080057</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,12 +1066,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar på gammal levande gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120474545</v>
+        <v>120474520</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1133,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750807</v>
+        <v>750809</v>
       </c>
       <c r="R6" t="n">
-        <v>7079863</v>
+        <v>7079547</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1302,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120474512</v>
+        <v>120474545</v>
       </c>
       <c r="B8" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>750695</v>
+        <v>750807</v>
       </c>
       <c r="R8" t="n">
-        <v>7080057</v>
+        <v>7079863</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,17 +1382,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar på gammal levande gran.</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120474544</v>
+        <v>120474515</v>
       </c>
       <c r="B9" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750779</v>
+        <v>750770</v>
       </c>
       <c r="R9" t="n">
-        <v>7079695</v>
+        <v>7079880</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spår i levande gran</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 21628-2021 artfynd.xlsx
+++ b/artfynd/A 21628-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120474544</v>
+        <v>120474519</v>
       </c>
       <c r="B2" t="n">
         <v>57373</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750779</v>
+        <v>750771</v>
       </c>
       <c r="R2" t="n">
-        <v>7079695</v>
+        <v>7079698</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spår i levande gran</t>
+          <t>Flera spår i levande gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120474521</v>
+        <v>120474513</v>
       </c>
       <c r="B3" t="n">
-        <v>97067</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750817</v>
+        <v>750669</v>
       </c>
       <c r="R3" t="n">
-        <v>7079478</v>
+        <v>7080068</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,17 +852,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1 kvm</t>
+          <t>Äldre hackspår i död gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120474516</v>
+        <v>120474544</v>
       </c>
       <c r="B4" t="n">
-        <v>90746</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750762</v>
+        <v>750779</v>
       </c>
       <c r="R4" t="n">
-        <v>7079867</v>
+        <v>7079695</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera kroppar på nyligen död gran</t>
+          <t>Spår i levande gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120474512</v>
+        <v>120474516</v>
       </c>
       <c r="B5" t="n">
         <v>90746</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750695</v>
+        <v>750762</v>
       </c>
       <c r="R5" t="n">
-        <v>7080057</v>
+        <v>7079867</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,17 +1066,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar på gammal levande gran.</t>
+          <t>Flera kroppar på nyligen död gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120474513</v>
+        <v>120474545</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750669</v>
+        <v>750807</v>
       </c>
       <c r="R7" t="n">
-        <v>7080068</v>
+        <v>7079863</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,17 +1275,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i död gran</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120474545</v>
+        <v>120474521</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>97067</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,25 +1319,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>750807</v>
+        <v>750817</v>
       </c>
       <c r="R8" t="n">
-        <v>7079863</v>
+        <v>7079478</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120474519</v>
+        <v>120474512</v>
       </c>
       <c r="B10" t="n">
-        <v>57373</v>
+        <v>90746</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750771</v>
+        <v>750695</v>
       </c>
       <c r="R10" t="n">
-        <v>7079698</v>
+        <v>7080057</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,17 +1586,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flera spår i levande gran</t>
+          <t>Flera fruktkroppar på gammal levande gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 21628-2021 artfynd.xlsx
+++ b/artfynd/A 21628-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120474519</v>
+        <v>120474544</v>
       </c>
       <c r="B2" t="n">
         <v>57373</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750771</v>
+        <v>750779</v>
       </c>
       <c r="R2" t="n">
-        <v>7079698</v>
+        <v>7079695</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Flera spår i levande gran</t>
+          <t>Spår i levande gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120474513</v>
+        <v>120474519</v>
       </c>
       <c r="B3" t="n">
         <v>57373</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750669</v>
+        <v>750771</v>
       </c>
       <c r="R3" t="n">
-        <v>7080068</v>
+        <v>7079698</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,17 +852,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre hackspår i död gran</t>
+          <t>Flera spår i levande gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120474544</v>
+        <v>120474515</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750779</v>
+        <v>750770</v>
       </c>
       <c r="R4" t="n">
-        <v>7079695</v>
+        <v>7079880</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spår i levande gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120474516</v>
+        <v>120474545</v>
       </c>
       <c r="B5" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750762</v>
+        <v>750807</v>
       </c>
       <c r="R5" t="n">
-        <v>7079867</v>
+        <v>7079863</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flera kroppar på nyligen död gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120474520</v>
+        <v>120474521</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>97067</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750809</v>
+        <v>750817</v>
       </c>
       <c r="R6" t="n">
-        <v>7079547</v>
+        <v>7079478</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120474545</v>
+        <v>120474513</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750807</v>
+        <v>750669</v>
       </c>
       <c r="R7" t="n">
-        <v>7079863</v>
+        <v>7080068</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,12 +1270,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i död gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120474521</v>
+        <v>120474516</v>
       </c>
       <c r="B8" t="n">
-        <v>97067</v>
+        <v>90746</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,25 +1319,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>750817</v>
+        <v>750762</v>
       </c>
       <c r="R8" t="n">
-        <v>7079478</v>
+        <v>7079867</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 kvm</t>
+          <t>Flera kroppar på nyligen död gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120474515</v>
+        <v>120474512</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750770</v>
+        <v>750695</v>
       </c>
       <c r="R9" t="n">
-        <v>7079880</v>
+        <v>7080057</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,12 +1484,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar på gammal levande gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120474512</v>
+        <v>120474520</v>
       </c>
       <c r="B10" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750695</v>
+        <v>750809</v>
       </c>
       <c r="R10" t="n">
-        <v>7080057</v>
+        <v>7079547</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,17 +1591,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar på gammal levande gran.</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 21628-2021 artfynd.xlsx
+++ b/artfynd/A 21628-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120474544</v>
+        <v>120474545</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750779</v>
+        <v>750807</v>
       </c>
       <c r="R2" t="n">
-        <v>7079695</v>
+        <v>7079863</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spår i levande gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120474515</v>
+        <v>120474512</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750770</v>
+        <v>750695</v>
       </c>
       <c r="R4" t="n">
-        <v>7079880</v>
+        <v>7080057</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,12 +954,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar på gammal levande gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120474545</v>
+        <v>120474521</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>97067</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750807</v>
+        <v>750817</v>
       </c>
       <c r="R5" t="n">
-        <v>7079863</v>
+        <v>7079478</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120474521</v>
+        <v>120474513</v>
       </c>
       <c r="B6" t="n">
-        <v>97067</v>
+        <v>57373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1110,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750817</v>
+        <v>750669</v>
       </c>
       <c r="R6" t="n">
-        <v>7079478</v>
+        <v>7080068</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,17 +1168,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1 kvm</t>
+          <t>Äldre hackspår i död gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120474513</v>
+        <v>120474544</v>
       </c>
       <c r="B7" t="n">
         <v>57373</v>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750669</v>
+        <v>750779</v>
       </c>
       <c r="R7" t="n">
-        <v>7080068</v>
+        <v>7079695</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,17 +1275,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre hackspår i död gran</t>
+          <t>Spår i levande gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120474516</v>
+        <v>120474520</v>
       </c>
       <c r="B8" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>750762</v>
+        <v>750809</v>
       </c>
       <c r="R8" t="n">
-        <v>7079867</v>
+        <v>7079547</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Flera kroppar på nyligen död gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120474512</v>
+        <v>120474515</v>
       </c>
       <c r="B9" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750695</v>
+        <v>750770</v>
       </c>
       <c r="R9" t="n">
-        <v>7080057</v>
+        <v>7079880</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,17 +1484,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar på gammal levande gran.</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120474520</v>
+        <v>120474516</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750809</v>
+        <v>750762</v>
       </c>
       <c r="R10" t="n">
-        <v>7079547</v>
+        <v>7079867</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,6 +1592,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Flera kroppar på nyligen död gran</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 21628-2021 artfynd.xlsx
+++ b/artfynd/A 21628-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120474545</v>
+        <v>120474544</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750807</v>
+        <v>750779</v>
       </c>
       <c r="R2" t="n">
-        <v>7079863</v>
+        <v>7079695</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spår i levande gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120474512</v>
+        <v>120474516</v>
       </c>
       <c r="B4" t="n">
         <v>90746</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750695</v>
+        <v>750762</v>
       </c>
       <c r="R4" t="n">
-        <v>7080057</v>
+        <v>7079867</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,17 +959,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar på gammal levande gran.</t>
+          <t>Flera kroppar på nyligen död gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120474521</v>
+        <v>120474545</v>
       </c>
       <c r="B5" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1008,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750817</v>
+        <v>750807</v>
       </c>
       <c r="R5" t="n">
-        <v>7079478</v>
+        <v>7079863</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120474513</v>
+        <v>120474521</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>97067</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1110,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750669</v>
+        <v>750817</v>
       </c>
       <c r="R6" t="n">
-        <v>7080068</v>
+        <v>7079478</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,17 +1168,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Äldre hackspår i död gran</t>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120474544</v>
+        <v>120474515</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750779</v>
+        <v>750770</v>
       </c>
       <c r="R7" t="n">
-        <v>7079695</v>
+        <v>7079880</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spår i levande gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120474520</v>
+        <v>120474512</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>750809</v>
+        <v>750695</v>
       </c>
       <c r="R8" t="n">
-        <v>7079547</v>
+        <v>7080057</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,12 +1377,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar på gammal levande gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120474515</v>
+        <v>120474520</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750770</v>
+        <v>750809</v>
       </c>
       <c r="R9" t="n">
-        <v>7079880</v>
+        <v>7079547</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120474516</v>
+        <v>120474513</v>
       </c>
       <c r="B10" t="n">
-        <v>90746</v>
+        <v>57373</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750762</v>
+        <v>750669</v>
       </c>
       <c r="R10" t="n">
-        <v>7079867</v>
+        <v>7080068</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,17 +1586,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flera kroppar på nyligen död gran</t>
+          <t>Äldre hackspår i död gran</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 21628-2021 artfynd.xlsx
+++ b/artfynd/A 21628-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120474544</v>
+        <v>120474519</v>
       </c>
       <c r="B2" t="n">
         <v>57373</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750779</v>
+        <v>750771</v>
       </c>
       <c r="R2" t="n">
-        <v>7079695</v>
+        <v>7079698</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spår i levande gran</t>
+          <t>Flera spår i levande gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120474519</v>
+        <v>120474521</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>97067</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750771</v>
+        <v>750817</v>
       </c>
       <c r="R3" t="n">
-        <v>7079698</v>
+        <v>7079478</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flera spår i levande gran</t>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120474545</v>
+        <v>120474544</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750807</v>
+        <v>750779</v>
       </c>
       <c r="R5" t="n">
-        <v>7079863</v>
+        <v>7079695</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spår i levande gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120474521</v>
+        <v>120474515</v>
       </c>
       <c r="B6" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1115,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750817</v>
+        <v>750770</v>
       </c>
       <c r="R6" t="n">
-        <v>7079478</v>
+        <v>7079880</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120474515</v>
+        <v>120474513</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750770</v>
+        <v>750669</v>
       </c>
       <c r="R7" t="n">
-        <v>7079880</v>
+        <v>7080068</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,12 +1275,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i död gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120474520</v>
+        <v>120474545</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1454,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750809</v>
+        <v>750807</v>
       </c>
       <c r="R9" t="n">
-        <v>7079547</v>
+        <v>7079863</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120474513</v>
+        <v>120474520</v>
       </c>
       <c r="B10" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750669</v>
+        <v>750809</v>
       </c>
       <c r="R10" t="n">
-        <v>7080068</v>
+        <v>7079547</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,17 +1591,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i död gran</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 21628-2021 artfynd.xlsx
+++ b/artfynd/A 21628-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120474519</v>
+        <v>120474516</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>90760</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750771</v>
+        <v>750762</v>
       </c>
       <c r="R2" t="n">
-        <v>7079698</v>
+        <v>7079867</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Flera spår i levande gran</t>
+          <t>Flera kroppar på nyligen död gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120474521</v>
+        <v>120474512</v>
       </c>
       <c r="B3" t="n">
-        <v>97067</v>
+        <v>90760</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750817</v>
+        <v>750695</v>
       </c>
       <c r="R3" t="n">
-        <v>7079478</v>
+        <v>7080057</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,17 +852,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1 kvm</t>
+          <t>Flera fruktkroppar på gammal levande gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120474516</v>
+        <v>120474544</v>
       </c>
       <c r="B4" t="n">
-        <v>90746</v>
+        <v>57381</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750762</v>
+        <v>750779</v>
       </c>
       <c r="R4" t="n">
-        <v>7079867</v>
+        <v>7079695</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera kroppar på nyligen död gran</t>
+          <t>Spår i levande gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120474544</v>
+        <v>120474520</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>78629</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750779</v>
+        <v>750809</v>
       </c>
       <c r="R5" t="n">
-        <v>7079695</v>
+        <v>7079547</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spår i levande gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1101,7 @@
         <v>120474515</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120474513</v>
+        <v>120474519</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750669</v>
+        <v>750771</v>
       </c>
       <c r="R7" t="n">
-        <v>7080068</v>
+        <v>7079698</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,17 +1270,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre hackspår i död gran</t>
+          <t>Flera spår i levande gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120474512</v>
+        <v>120474513</v>
       </c>
       <c r="B8" t="n">
-        <v>90746</v>
+        <v>57381</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>750695</v>
+        <v>750669</v>
       </c>
       <c r="R8" t="n">
-        <v>7080057</v>
+        <v>7080068</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar på gammal levande gran.</t>
+          <t>Äldre hackspår i död gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120474545</v>
+        <v>120474521</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>97085</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1431,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750807</v>
+        <v>750817</v>
       </c>
       <c r="R9" t="n">
-        <v>7079863</v>
+        <v>7079478</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,6 +1490,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120474520</v>
+        <v>120474545</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750809</v>
+        <v>750807</v>
       </c>
       <c r="R10" t="n">
-        <v>7079547</v>
+        <v>7079863</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 21628-2021 artfynd.xlsx
+++ b/artfynd/A 21628-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120474516</v>
+        <v>120474512</v>
       </c>
       <c r="B2" t="n">
-        <v>90760</v>
+        <v>90762</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750762</v>
+        <v>750695</v>
       </c>
       <c r="R2" t="n">
-        <v>7079867</v>
+        <v>7080057</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Flera kroppar på nyligen död gran</t>
+          <t>Flera fruktkroppar på gammal levande gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120474512</v>
+        <v>120474515</v>
       </c>
       <c r="B3" t="n">
-        <v>90760</v>
+        <v>78631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750695</v>
+        <v>750770</v>
       </c>
       <c r="R3" t="n">
-        <v>7080057</v>
+        <v>7079880</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,17 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar på gammal levande gran.</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120474544</v>
+        <v>120474513</v>
       </c>
       <c r="B4" t="n">
         <v>57381</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750779</v>
+        <v>750669</v>
       </c>
       <c r="R4" t="n">
-        <v>7079695</v>
+        <v>7080068</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,17 +954,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spår i levande gran</t>
+          <t>Äldre hackspår i död gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120474520</v>
+        <v>120474544</v>
       </c>
       <c r="B5" t="n">
-        <v>78629</v>
+        <v>57381</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750809</v>
+        <v>750779</v>
       </c>
       <c r="R5" t="n">
-        <v>7079547</v>
+        <v>7079695</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spår i levande gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120474515</v>
+        <v>120474519</v>
       </c>
       <c r="B6" t="n">
-        <v>78629</v>
+        <v>57381</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750770</v>
+        <v>750771</v>
       </c>
       <c r="R6" t="n">
-        <v>7079880</v>
+        <v>7079698</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera spår i levande gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120474519</v>
+        <v>120474545</v>
       </c>
       <c r="B7" t="n">
-        <v>57381</v>
+        <v>78631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750771</v>
+        <v>750807</v>
       </c>
       <c r="R7" t="n">
-        <v>7079698</v>
+        <v>7079863</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flera spår i levande gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120474513</v>
+        <v>120474516</v>
       </c>
       <c r="B8" t="n">
-        <v>57381</v>
+        <v>90762</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>750669</v>
+        <v>750762</v>
       </c>
       <c r="R8" t="n">
-        <v>7080068</v>
+        <v>7079867</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,17 +1377,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre hackspår i död gran</t>
+          <t>Flera kroppar på nyligen död gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120474521</v>
+        <v>120474520</v>
       </c>
       <c r="B9" t="n">
-        <v>97085</v>
+        <v>78631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750817</v>
+        <v>750809</v>
       </c>
       <c r="R9" t="n">
-        <v>7079478</v>
+        <v>7079547</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120474545</v>
+        <v>120474521</v>
       </c>
       <c r="B10" t="n">
-        <v>78629</v>
+        <v>97087</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1533,25 +1528,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750807</v>
+        <v>750817</v>
       </c>
       <c r="R10" t="n">
-        <v>7079863</v>
+        <v>7079478</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,6 +1592,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD10" t="b">
